--- a/Documents/Can Converter Unit v2.xlsx
+++ b/Documents/Can Converter Unit v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\pcb-stm32-can-converter-v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\pcb-stm32-can-converter-v2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7D3A5F8-35F0-41D6-98A2-3B3CFEDC1E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033C5A2C-8088-4947-903A-2BC027854270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C52BD6FB-3D92-4C84-8589-E2D66043FFAF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t>DC/DC</t>
   </si>
@@ -80,9 +80,6 @@
     <t>M12 kątowe</t>
   </si>
   <si>
-    <t>12 to 5V 2A</t>
-  </si>
-  <si>
     <t>Pomiar prądu + napięcia?</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>jak działa taki dławik i czy go wstawiać</t>
   </si>
   <si>
-    <t>dioda idealna?</t>
-  </si>
-  <si>
     <t>Fuse 12 V na każde wyjście</t>
   </si>
   <si>
@@ -242,9 +236,6 @@
     <t>toleruje od -12 do 12V i +-14V na diff</t>
   </si>
   <si>
-    <t>Pmosfet</t>
-  </si>
-  <si>
     <t>TVS do RS</t>
   </si>
   <si>
@@ -267,13 +258,31 @@
   </si>
   <si>
     <t>zjawisko millera MOSFET</t>
+  </si>
+  <si>
+    <t>https://www.mouser.pl/ProductDetail/Texas-Instruments/LMR51625YFDDCR?qs=efUn273yAhe0Di9PgWnVVg%3D%3D</t>
+  </si>
+  <si>
+    <t>LMR51625YFDDCR</t>
+  </si>
+  <si>
+    <t>Apka TI:</t>
+  </si>
+  <si>
+    <t>transil TVS</t>
+  </si>
+  <si>
+    <t>JAKI DRYFT TEMPERATUROWY</t>
+  </si>
+  <si>
+    <t>jak obliczyć C do rezonatorów</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +317,21 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -330,11 +354,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -357,16 +385,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>314326</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>151494</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>350185</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>8058</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>428626</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>28784</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>464485</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>64643</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -389,8 +417,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12382501" y="4151994"/>
-          <a:ext cx="1943100" cy="1020290"/>
+          <a:off x="9843809" y="4131823"/>
+          <a:ext cx="1943100" cy="953055"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -401,16 +429,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>99560</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>88866</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1883536</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>70936</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>122480</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>156882</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>606574</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>138951</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -433,8 +461,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5467178" y="4279866"/>
-          <a:ext cx="4527684" cy="2925516"/>
+          <a:off x="5487348" y="4553289"/>
+          <a:ext cx="4612850" cy="2757427"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>242047</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19503</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>120668</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>124913</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Obraz 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32EB5C5A-78CA-79ED-E541-DE0185F5BCA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11564471" y="557385"/>
+          <a:ext cx="4755421" cy="1898352"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -763,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F870EDE-6DF7-4595-B839-DFBF3E74AA35}">
-  <dimension ref="A2:R47"/>
+  <dimension ref="A2:R48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.5546875" customWidth="1"/>
@@ -772,7 +844,7 @@
     <col min="4" max="4" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -780,7 +852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -791,7 +863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -799,69 +871,72 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>0</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -870,7 +945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -881,211 +956,229 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" t="s">
         <v>23</v>
       </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
+      <c r="H16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" t="s">
         <v>27</v>
       </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="J28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H16:K17"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{0813BD0A-35C6-461C-B52E-3850A74C5221}"/>
     <hyperlink ref="C13" r:id="rId2" xr:uid="{36D84A23-138D-4A4E-B230-4ED46E4CB37D}"/>
@@ -1100,10 +1193,12 @@
     <hyperlink ref="F16" r:id="rId11" xr:uid="{66813B4B-9D82-4057-8414-D516D48D05CB}"/>
     <hyperlink ref="C16" r:id="rId12" xr:uid="{E990F98A-1D51-4089-8CFF-98C7C52A5BB6}"/>
     <hyperlink ref="C10" r:id="rId13" xr:uid="{51162D4E-D42C-4208-93B0-AF1433405CF8}"/>
+    <hyperlink ref="F12" r:id="rId14" xr:uid="{A18A127C-91B1-4727-8A13-F35F6DF0961C}"/>
+    <hyperlink ref="C12" r:id="rId15" xr:uid="{2559718E-051A-4A90-8832-06C025945A8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" r:id="rId14"/>
-  <drawing r:id="rId15"/>
+  <pageSetup paperSize="0" orientation="portrait" r:id="rId16"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
